--- a/docs/telnyx-test-plan.xlsx
+++ b/docs/telnyx-test-plan.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Cases'!$A$1:$N$16</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Cases'!$A$1:$O$16</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="180">
   <si>
     <t xml:space="preserve">Telnyx.com UI Test Plan — Cypress + Cucumber</t>
   </si>
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Version / Date</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0 / 2026-10-22</t>
+    <t xml:space="preserve">1.1 / 2026-10-23</t>
   </si>
   <si>
     <t xml:space="preserve">Objective</t>
@@ -89,16 +89,17 @@
   </si>
   <si>
     <t xml:space="preserve">• BDD: Gherkin .feature files grouped by site area + step definitions
-• Page Object pattern for locators and actions
-• Test data (navigation items, social URLs) in fixtures
-• Tags: @smoke for the critical path, @regression for the full suite
-• Assertions target stable visible content and semantic attributes (href, target, aria-expanded, data-state)</t>
+• Page Object pattern: pages extend BasePage; the site-wide header and footer are separate components
+• Test data (navigation items, social URLs, emails, expected messages) in Gherkin data tables and step parameters
+• Tags: @TC-xxx for each test case, @smoke for the critical path, @regression for the full suite
+• Links are found by their visible text, and the href is asserted separately
+• Assertions target stable visible content and semantic attributes (href, target, aria-expanded)</t>
   </si>
   <si>
     <t xml:space="preserve">Known site behaviour</t>
   </si>
   <si>
-    <t xml:space="preserve">telnyx.com throws its own uncaught errors (document.modelContext SecurityError, cross-origin 'Script error.'). Only these are ignored in cypress/support/e2e.js; any other application error still fails the test. The OneTrust cookie banner is suppressed by setting consent cookies before each test.</t>
+    <t xml:space="preserve">telnyx.com throws its own uncaught errors (document.modelContext SecurityError, cross-origin 'Script error.'). Only these are ignored in cypress/support/e2e.ts; any other application error still fails the test. The OneTrust cookie banner is suppressed by setting consent cookies before each test.</t>
   </si>
   <si>
     <t xml:space="preserve">Environment</t>
@@ -113,25 +114,25 @@
     <t xml:space="preserve">Browsers</t>
   </si>
   <si>
-    <t xml:space="preserve">Chrome (primary, CI), Electron (Cypress default); desktop viewport 1440 × 900, mobile viewport 375 × 812</t>
+    <t xml:space="preserve">Chrome (local runs and CI); desktop viewport 1440 × 900, mobile viewport 375 × 812 (Cypress iphone-x preset)</t>
   </si>
   <si>
     <t xml:space="preserve">Tools</t>
   </si>
   <si>
-    <t xml:space="preserve">Node.js LTS, Cypress, @badeball/cypress-cucumber-preprocessor, esbuild, HTML report (cucumber/mochawesome), GitHub Actions, GitHub Pages</t>
+    <t xml:space="preserve">Node.js 24, Cypress, TypeScript, @badeball/cypress-cucumber-preprocessor, esbuild, Cucumber HTML report (built into the preprocessor), ESLint + Prettier, GitHub Actions, GitHub Pages</t>
   </si>
   <si>
     <t xml:space="preserve">Configuration</t>
   </si>
   <si>
-    <t xml:space="preserve">Base config cypress.config.js plus a separate environment config file (e.g. cypress.prod.config.js) selected with --config-file; base URL configurable.</t>
+    <t xml:space="preserve">Base config cypress.config.ts for local runs (no retries) plus cypress.ci.config.ts for GitHub Actions (longer timeouts, 2 retries), selected with --config-file.</t>
   </si>
   <si>
     <t xml:space="preserve">CI / Reporting</t>
   </si>
   <si>
-    <t xml:space="preserve">GitHub Actions runs the suite on push / pull request / manual trigger, uploads screenshots on failure, generates an HTML report and publishes it to GitHub Pages.</t>
+    <t xml:space="preserve">GitHub Actions runs on push to main, pull requests and manual trigger: type check, lint, format check, tests. Screenshots and the HTML report are uploaded as artifacts on every run; on main the report is published to GitHub Pages.</t>
   </si>
   <si>
     <t xml:space="preserve">Criteria</t>
@@ -210,6 +211,9 @@
     <t xml:space="preserve">Comments</t>
   </si>
   <si>
+    <t xml:space="preserve">Last run</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC-001</t>
   </si>
   <si>
@@ -237,10 +241,11 @@
     <t xml:space="preserve">URL: https://telnyx.com/</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open https://telnyx.com/.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The homepage loads and the browser URL is https://telnyx.com/.</t>
+    <t xml:space="preserve">1. Open https://telnyx.com/.
+2. Check the URL, the site header and the main heading.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The browser URL is https://telnyx.com/ and the site header and the main heading are displayed.</t>
   </si>
   <si>
     <t xml:space="preserve">Yes</t>
@@ -249,10 +254,13 @@
     <t xml:space="preserve">Passed</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-10-22, CI run #1</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC-002</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify logo is visible and navigates to homepage</t>
+    <t xml:space="preserve">Verify logo navigates to homepage</t>
   </si>
   <si>
     <t xml:space="preserve">Medium</t>
@@ -264,18 +272,18 @@
     <t xml:space="preserve">@regression</t>
   </si>
   <si>
-    <t xml:space="preserve">Homepage is open; cookie banner is suppressed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logo link href: /</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate the Telnyx logo in the site header.
-2. Verify it is visible and links to '/'.
+    <t xml:space="preserve">Pricing page is open; cookie banner is suppressed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start page: /pricing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open https://telnyx.com/pricing.
+2. Verify the Telnyx logo is visible in the site header.
 3. Click the logo.</t>
   </si>
   <si>
-    <t xml:space="preserve">The logo is visible, has the homepage link, and clicking it opens https://telnyx.com/.</t>
+    <t xml:space="preserve">Clicking the logo opens https://telnyx.com/ with the site header and the main heading displayed.</t>
   </si>
   <si>
     <t xml:space="preserve">TC-003</t>
@@ -321,15 +329,19 @@
     <t xml:space="preserve">Navigation</t>
   </si>
   <si>
-    <t xml:space="preserve">Expected URL part: /sign-up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click the Sign up link in the header.
-2. Wait for the registration page to load.
+    <t xml:space="preserve">Homepage is open; cookie banner is suppressed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected href: /sign-up
+Expected heading: Create your account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Find the Sign up link in the header by its text and check its href.
+2. Click the link.
 3. Check the page URL and heading.</t>
   </si>
   <si>
-    <t xml:space="preserve">The URL contains '/sign-up' and the 'Create your account' heading is displayed.</t>
+    <t xml:space="preserve">The link points to /sign-up, the URL contains '/sign-up' and the 'Create your account' heading is displayed.</t>
   </si>
   <si>
     <t xml:space="preserve">TC-005</t>
@@ -341,7 +353,7 @@
     <t xml:space="preserve">Expected href: https://portal.telnyx.com</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Verify the Log in link is visible and points to https://portal.telnyx.com.
+    <t xml:space="preserve">1. Find the Log in link in the header by its text; verify it is visible and points to https://portal.telnyx.com.
 2. Click the link (opened in the same tab for the test).
 3. Verify the portal sign-in page opens.</t>
   </si>
@@ -498,15 +510,15 @@
     <t xml:space="preserve">Verify mobile navigation menu opens</t>
   </si>
   <si>
-    <t xml:space="preserve">Viewport is set to 375 × 812; homepage is open; cookie banner is suppressed.</t>
+    <t xml:space="preserve">Viewport is set to 375 × 812 (iphone-x); homepage is open; cookie banner is suppressed.</t>
   </si>
   <si>
     <t xml:space="preserve">Viewport: 375 × 812</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open the homepage at mobile viewport size.
-2. Locate the mobile menu button.
-3. Click the button.
+2. Verify the mobile menu button is visible and the menu is closed.
+3. Open the mobile menu.
 4. Verify the navigation menu is open.</t>
   </si>
   <si>
@@ -525,10 +537,9 @@
     <t xml:space="preserve">Dropdowns: Products, Solutions</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open the Products dropdown.
-2. Verify it is expanded.
-3. Open the Solutions dropdown.
-4. Check the expanded state of both dropdowns.</t>
+    <t xml:space="preserve">1. Open the Products dropdown and verify it is expanded.
+2. Open the Solutions dropdown.
+3. Check the expanded state of both dropdowns.</t>
   </si>
   <si>
     <t xml:space="preserve">Solutions has aria-expanded='true' and Products has aria-expanded='false'.</t>
@@ -575,8 +586,8 @@
 Terms checkbox: checked</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Enter an invalid email.
-2. Accept the terms checkbox to isolate email validation.
+    <t xml:space="preserve">1. Accept the terms checkbox to isolate email validation.
+2. Enter an invalid email.
 3. Click Create account.
 4. Inspect the email validation message.</t>
   </si>
@@ -587,7 +598,7 @@
     <t xml:space="preserve">Test Summary</t>
   </si>
   <si>
-    <t xml:space="preserve">Counts update automatically from the Status column on the Test Cases sheet.</t>
+    <t xml:space="preserve">Counts are COUNTIF formulas over the Priority, Area and Status columns of the Test Cases sheet.</t>
   </si>
   <si>
     <t xml:space="preserve">Test cases</t>
@@ -616,7 +627,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -672,6 +683,14 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -775,16 +794,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -804,11 +827,15 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -825,7 +852,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -877,6 +904,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0563C1"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -948,7 +983,7 @@
       <rgbColor rgb="FFFFE699"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FF0563C1"/>
       <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -999,34 +1034,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1037,69 +1072,11 @@
         <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -1230,193 +1207,193 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="110"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="110"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+    <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="B7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="B10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+    <row r="12" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+    <row r="13" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="B14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+    <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="B20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+    <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1446,718 +1423,767 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:O16"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="4" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="L2" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="N2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="M2" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="N2" s="5"/>
+      <c r="O2" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N3" s="5"/>
+      <c r="O3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="4" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="5"/>
+      <c r="O4" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N5" s="5"/>
+      <c r="O5" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N6" s="5"/>
+      <c r="O6" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N7" s="5"/>
+      <c r="O7" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N8" s="5"/>
+      <c r="O8" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="F9" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M3" s="6" t="s">
+      <c r="H9" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="L9" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="N3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="M9" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N9" s="5"/>
+      <c r="O9" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N10" s="5"/>
+      <c r="O10" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N11" s="5"/>
+      <c r="O11" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N12" s="5"/>
+      <c r="O12" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N13" s="5"/>
+      <c r="O13" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M4" s="6" t="s">
+      <c r="D14" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="L14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="N4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M5" s="6" t="s">
+      <c r="M14" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N14" s="5"/>
+      <c r="O14" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L15" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="N5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M6" s="6" t="s">
+      <c r="M15" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N15" s="5"/>
+      <c r="O15" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="L16" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="N6" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="N7" s="4"/>
-    </row>
-    <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="N8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="N9" s="4"/>
-    </row>
-    <row r="10" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="N10" s="4"/>
-    </row>
-    <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="N11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="N12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="N13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="N14" s="4"/>
-    </row>
-    <row r="15" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="N15" s="4"/>
-    </row>
-    <row r="16" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="N16" s="4"/>
+      <c r="M16" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N16" s="5"/>
+      <c r="O16" s="8" t="s">
+        <v>69</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N16"/>
+  <autoFilter ref="A1:O16"/>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"High"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>"Medium"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>"Low"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M16">
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>"Passed"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2167,6 +2193,23 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="O2" r:id="rId1" display="2026-10-22, CI run #1"/>
+    <hyperlink ref="O3" r:id="rId2" display="2026-10-22, CI run #1"/>
+    <hyperlink ref="O4" r:id="rId3" display="2026-10-22, CI run #1"/>
+    <hyperlink ref="O5" r:id="rId4" display="2026-10-22, CI run #1"/>
+    <hyperlink ref="O6" r:id="rId5" display="2026-10-22, CI run #1"/>
+    <hyperlink ref="O7" r:id="rId6" display="2026-10-22, CI run #1"/>
+    <hyperlink ref="O8" r:id="rId7" display="2026-10-22, CI run #1"/>
+    <hyperlink ref="O9" r:id="rId8" display="2026-10-22, CI run #1"/>
+    <hyperlink ref="O10" r:id="rId9" display="2026-10-22, CI run #1"/>
+    <hyperlink ref="O11" r:id="rId10" display="2026-10-22, CI run #1"/>
+    <hyperlink ref="O12" r:id="rId11" display="2026-10-22, CI run #1"/>
+    <hyperlink ref="O13" r:id="rId12" display="2026-10-22, CI run #1"/>
+    <hyperlink ref="O14" r:id="rId13" display="2026-10-22, CI run #1"/>
+    <hyperlink ref="O15" r:id="rId14" display="2026-10-22, CI run #1"/>
+    <hyperlink ref="O16" r:id="rId15" display="2026-10-22, CI run #1"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2174,7 +2217,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId16"/>
 </worksheet>
 </file>
 
@@ -2184,204 +2227,204 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="4" t="n">
+      <c r="B4" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="5" t="n">
         <f aca="false">COUNTIF('Test Cases'!$E$2:$E$16,A5)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="4" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="5" t="n">
         <f aca="false">COUNTIF('Test Cases'!$E$2:$E$16,A6)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B7" s="4" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="5" t="n">
         <f aca="false">COUNTIF('Test Cases'!$E$2:$E$16,A7)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B8" s="3" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="4" t="n">
         <f aca="false">SUM(B5:B7)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="4" t="n">
+      <c r="B10" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="5" t="n">
         <f aca="false">COUNTIF('Test Cases'!$C$2:$C$16,A11)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" s="4" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="5" t="n">
         <f aca="false">COUNTIF('Test Cases'!$C$2:$C$16,A12)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="4" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="5" t="n">
         <f aca="false">COUNTIF('Test Cases'!$C$2:$C$16,A13)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B14" s="4" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="5" t="n">
         <f aca="false">COUNTIF('Test Cases'!$C$2:$C$16,A14)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B15" s="4" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" s="5" t="n">
         <f aca="false">COUNTIF('Test Cases'!$C$2:$C$16,A15)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B16" s="4" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" s="5" t="n">
         <f aca="false">COUNTIF('Test Cases'!$C$2:$C$16,A16)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B17" s="4" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B17" s="5" t="n">
         <f aca="false">COUNTIF('Test Cases'!$C$2:$C$16,A17)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B18" s="3" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B18" s="4" t="n">
         <f aca="false">SUM(B11:B17)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B21" s="4" t="n">
+      <c r="B20" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" s="5" t="n">
         <f aca="false">COUNTIF('Test Cases'!$M$2:$M$16,A21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B22" s="4" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="5" t="n">
         <f aca="false">COUNTIF('Test Cases'!$M$2:$M$16,A22)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B23" s="4" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B23" s="5" t="n">
         <f aca="false">COUNTIF('Test Cases'!$M$2:$M$16,A23)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B24" s="4" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B24" s="5" t="n">
         <f aca="false">COUNTIF('Test Cases'!$M$2:$M$16,A24)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B25" s="3" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B25" s="4" t="n">
         <f aca="false">SUM(B21:B24)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B27" s="9" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B27" s="11" t="n">
         <f aca="false">IFERROR(COUNTIF('Test Cases'!$M$2:$M$16,"Passed")/COUNTA('Test Cases'!$A$2:$A$16),0)</f>
         <v>1</v>
       </c>

--- a/docs/telnyx-test-plan.xlsx
+++ b/docs/telnyx-test-plan.xlsx
@@ -376,15 +376,17 @@
     <t xml:space="preserve">Homepage is open in desktop viewport; cookie banner is suppressed.</t>
   </si>
   <si>
-    <t xml:space="preserve">Expected URL part: /pricing</t>
+    <t xml:space="preserve">Expected href: /pricing
+Expected heading: Pay for what you use</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open the Pricing menu in the header.
-2. Click the link to view all pricing.
-3. Verify the URL and page content.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The browser navigates to '/pricing' and the pricing page content is displayed.</t>
+2. Find the View all pricing link by its text and check its href.
+3. Click the link.
+4. Check the page URL and heading.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The link points to /pricing, the URL contains '/pricing' and the 'Pay for what you use.' heading is displayed.</t>
   </si>
   <si>
     <t xml:space="preserve">TC-007</t>
